--- a/src/attributions/attributions_ig_traj_18.xlsx
+++ b/src/attributions/attributions_ig_traj_18.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005477941338775934</v>
+        <v>-0.0292495741370862</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04812546559841871</v>
+        <v>0.07203728843223832</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1292359597042983</v>
+        <v>-0.0561166207615129</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02997226516312941</v>
+        <v>0.09831288162418482</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006380989567265621</v>
+        <v>0.006129395504446462</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01050566878282411</v>
+        <v>-0.005858703551172461</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05837643995742314</v>
+        <v>-0.01943609088791551</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.02349673686539263</v>
+        <v>0.03698584524891002</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1189162319340324</v>
+        <v>-0.06524805466652887</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1643,52 +1643,52 @@
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1763417936789596</v>
+        <v>0.07741262833195306</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02717170699305905</v>
+        <v>-0.07525809727643185</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07008265260948662</v>
+        <v>-0.05756196773596754</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.02278641978096671</v>
+        <v>0.008810068560588228</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.04653651181406477</v>
+        <v>-0.0463749112874411</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1166646606034977</v>
+        <v>-0.0660848896381761</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1700,49 +1700,49 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.005481498336917178</v>
+        <v>-0.09787623622891735</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2008055535126371</v>
+        <v>0.02438757624247902</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.09391298633215867</v>
+        <v>-0.262351122347062</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.006633193721945011</v>
+        <v>-0.005631543202471633</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03806093890753613</v>
+        <v>0.009086656019379923</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02193693455930493</v>
+        <v>0.02378297184657251</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,49 +1754,49 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03899343110147304</v>
+        <v>0.06038714480682483</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.01205414052650297</v>
+        <v>-0.000208439332801203</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3006498554134087</v>
+        <v>0.02192484377468341</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1096307056207893</v>
+        <v>-0.1041565321764039</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1421868425350084</v>
+        <v>0.1148294535542177</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.07628306544576788</v>
+        <v>-0.1158363169763028</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1805,52 +1805,52 @@
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0007758227681215805</v>
+        <v>0.0600020314817557</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.01834860736828823</v>
+        <v>-0.02220676170433628</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.06657034125120143</v>
+        <v>0.06965539544891963</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.0255559074515273</v>
+        <v>-0.03618278831135686</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.09221771728330862</v>
+        <v>0.002968425754330726</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.1596158157608103</v>
+        <v>-0.01351387235813504</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,52 +1859,52 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.005655460473038792</v>
+        <v>0.04799090709091137</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.004153497921191774</v>
+        <v>-0.03968317032947509</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.05027554504720716</v>
+        <v>0.02795401235652571</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.009484008573486309</v>
+        <v>0.04263911782442219</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.001414971181088745</v>
+        <v>0.0005468335848967804</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01306208789560892</v>
+        <v>0.1446624199282601</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1913,82 +1913,82 @@
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.01257340222205711</v>
+        <v>0.07927171870381866</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.06748410474515136</v>
+        <v>0.0291873567658834</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1674290122768674</v>
+        <v>-0.09479259366776589</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.05360077697838679</v>
+        <v>0.02401607551390334</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.02120090099364941</v>
+        <v>0.1396029531910916</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0255894420028676</v>
+        <v>-0.09228440559258641</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0002584784280895621</v>
+        <v>0.0320507794242718</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.04609749073463212</v>
+        <v>0.01230070781058659</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.02337515335381379</v>
+        <v>0.06778564123574771</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0196249234214589</v>
+        <v>0.01210016290609288</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.008439039910776942</v>
+        <v>-0.01382997022972459</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.00798138043992846</v>
+        <v>0.103657661737219</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,25 +2027,25 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01244214858680019</v>
+        <v>0.04560409202434625</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.004779776682157</v>
+        <v>-0.03906815669258824</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02955777757758325</v>
+        <v>0.04687271308722624</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,46 +2054,46 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06779655754249699</v>
+        <v>0.1699879060141691</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.05048241391964107</v>
+        <v>0.03364737993535241</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.06280446414071045</v>
+        <v>-0.01912700137492231</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03205673298410638</v>
+        <v>0.1365365012464572</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0009664898682797829</v>
+        <v>0.001607513225300346</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.007023974964147773</v>
+        <v>0.006524100299785523</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,31 +2105,31 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03918818252876251</v>
+        <v>0.1432596221884573</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0.01105861600526938</v>
+        <v>0.0009109791026554459</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1702680342183941</v>
+        <v>0.1606845934090893</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03750938105714418</v>
+        <v>-0.03934213634403482</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04151177740397298</v>
+        <v>-0.03127334061334316</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04445575573872908</v>
+        <v>0.05827974546748781</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05792678938622739</v>
+        <v>0.07175089233206373</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.008000713065079445</v>
+        <v>-0.005538226992285258</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2191,73 +2191,73 @@
         <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1192044707820182</v>
+        <v>0.03737988821911258</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04289676600986223</v>
+        <v>-0.02642334036878648</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06025344419237787</v>
+        <v>-0.0187921531505994</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04133870673831443</v>
+        <v>-0.003589976148031014</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.02101541921288603</v>
+        <v>-0.06292129457026771</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0235061069576187</v>
+        <v>-0.06443579880846491</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03345255109534338</v>
+        <v>0.07655016510032164</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03577898719404407</v>
+        <v>-0.02786534227772766</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.005584082972208834</v>
+        <v>0.04344896146160228</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.324056217410337</v>
+        <v>0.2515412291765233</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01356180571905595</v>
+        <v>-0.06050308883225695</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1767902254617536</v>
+        <v>-0.1074910971949254</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.001287139071835842</v>
+        <v>-0.009095483696108336</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.03685541381653606</v>
+        <v>-0.009843146947421888</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.04746680849025501</v>
+        <v>-0.009323661947222891</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.0009288281276884004</v>
+        <v>-0.01502587860768515</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08055637825571149</v>
+        <v>0.02840139696636316</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01688265111630071</v>
+        <v>0.05463203153015787</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,16 +2356,16 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.181521825659493</v>
+        <v>0.175874376318464</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01935646858250013</v>
+        <v>-0.04964523655769941</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02593379431716398</v>
+        <v>-0.01224095160088981</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -2374,61 +2374,61 @@
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05625063762045156</v>
+        <v>-0.08942740515698516</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002389776894128779</v>
+        <v>0.07049633833363665</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.009986047430297663</v>
+        <v>0.006439548741170673</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02185189616310797</v>
+        <v>-0.07115752094195194</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.09550880876112032</v>
+        <v>0.08859627933349563</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1325268132514904</v>
+        <v>0.0253597502144192</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.04842759354443942</v>
+        <v>-0.095927348409747</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02712311780764276</v>
+        <v>0.07925223809212795</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.004478396080718345</v>
+        <v>0.01406453783491449</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05749569831445638</v>
+        <v>-0.04014200610994464</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.00126642326402304</v>
+        <v>-0.004921890052420837</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0004962456823940298</v>
+        <v>0.001422896697721378</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07837551724248633</v>
+        <v>-0.07053586171562094</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03484013414967994</v>
+        <v>0.03872006268517179</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.01928077990777129</v>
+        <v>-0.03866438609636583</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05145734396617425</v>
+        <v>0.01023861237314646</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.064335452643265</v>
+        <v>0.03680148234751825</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01167406410748823</v>
+        <v>-0.01138033261253902</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,22 +2539,22 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.03201651854765751</v>
+        <v>-0.05951432260217013</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.06346051269666618</v>
+        <v>0.05606265254809278</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.005714945954477186</v>
+        <v>0.02680313338632296</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
@@ -2563,79 +2563,79 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02280636339291503</v>
+        <v>-0.04987677376807387</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.02493103171925124</v>
+        <v>-0.03808687955768254</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.005139448325726882</v>
+        <v>-0.004101338510519519</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.04718100075590072</v>
+        <v>-0.1029591836783795</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.009842821304555344</v>
+        <v>0.07666415658287942</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02208396987039721</v>
+        <v>0.00486077435076053</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.02196970900495943</v>
+        <v>-0.05715337442183017</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03867267205531605</v>
+        <v>0.03068739669193043</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01372533997481111</v>
+        <v>0.002992247108138505</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
@@ -2647,61 +2647,61 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0005172553760487576</v>
+        <v>8.671410251717683e-05</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001392519314997309</v>
+        <v>0.106546937735315</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0005964273569846559</v>
+        <v>-0.0009506990197407871</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.005256614517789434</v>
+        <v>-0.0695666997582528</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.01965665283296</v>
+        <v>0.02592484975889789</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02910508709710302</v>
+        <v>0.3633256587045675</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02719018858758708</v>
+        <v>0.05891230865376676</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02163269228189662</v>
+        <v>-0.1870638152301316</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004610547531083419</v>
+        <v>0.1724163764518783</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.008429574979292991</v>
+        <v>-0.0118634732170895</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002868329182419681</v>
+        <v>0.02807273474432983</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.005241455588618308</v>
+        <v>0.1749392383616207</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,37 +2772,37 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01600470448164149</v>
+        <v>-0.1757661104174194</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01678266665590853</v>
+        <v>0.0109805905844446</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01517324685152308</v>
+        <v>-0.01632107724866924</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01117262044730659</v>
+        <v>-0.2823952623296842</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01099134884984442</v>
+        <v>-0.03739258863142809</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2811,13 +2811,13 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.00487695612261039</v>
+        <v>0.1057503566906129</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01059833957154258</v>
+        <v>0.09334422505793916</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003896223220294401</v>
+        <v>-0.0879578132679866</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.03905056867369019</v>
+        <v>0.671167476732626</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03917404673052311</v>
+        <v>-0.1977229822962281</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01307948149022929</v>
+        <v>-0.2637009445794663</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,19 +2871,19 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00924011178388</v>
+        <v>-0.0007774619897782122</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.006869787526253931</v>
+        <v>-0.03771769710336952</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.0049456055086821</v>
+        <v>-0.03468635152692941</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02970815190337998</v>
+        <v>0.01747184545973727</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01267790523371823</v>
+        <v>0.1056487388761345</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.00518547298531445</v>
+        <v>0.146707242286805</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01417225936244665</v>
+        <v>0.5035018208081096</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02123172535752216</v>
+        <v>-0.02153516973731642</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.004607409079406578</v>
+        <v>-0.157157258214447</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003195352772099748</v>
+        <v>-0.1952166674481956</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01021053260391885</v>
+        <v>-0.04086260574468365</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01191783822372096</v>
+        <v>0.1517960739138902</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,10 +2976,10 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.002527257226687133</v>
+        <v>-0.2677731028669956</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,40 +2988,40 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.004133818867855252</v>
+        <v>0.1707427637281959</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.002116796450177274</v>
+        <v>0.1220182054483397</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001469503369822709</v>
+        <v>-0.1846168255192719</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.009823954736655718</v>
+        <v>-0.04910525941401723</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01569354879975735</v>
+        <v>0.1455080530529011</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01108018786274812</v>
+        <v>-0.05671902119210314</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01252648145789864</v>
+        <v>-0.1146972436755552</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.0009984141758186968</v>
+        <v>0.01752658166813045</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.006206573797542386</v>
+        <v>-0.1017501469316677</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01659748282713291</v>
+        <v>0.01047487344751647</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.008572193394684352</v>
+        <v>0.01267358055965425</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01193382048173978</v>
+        <v>0.01058831174061014</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01363156415902247</v>
+        <v>-0.0409385420333116</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.003605460695087642</v>
+        <v>0.142109525143342</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,7 +3114,7 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001053355074503144</v>
+        <v>-0.05815059248956043</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
@@ -3123,25 +3123,25 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.006599061497596774</v>
+        <v>-0.130879415799854</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01295874462756225</v>
+        <v>0.02499024171059862</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.007208696664175946</v>
+        <v>-0.07893355588799204</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0213652062083301</v>
+        <v>-0.2050281463306263</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.007893052765281239</v>
+        <v>0.1020062644349683</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003852359878142634</v>
+        <v>-0.1931308299693234</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.009714600393057994</v>
+        <v>-0.08794781430133201</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01430589164085029</v>
+        <v>0.1150729865952197</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,34 +3195,34 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0134204974989969</v>
+        <v>-0.2321684304885063</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02505046305129288</v>
+        <v>0.04980461423111743</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0133901510743258</v>
+        <v>0.1599657198527782</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002055784878975518</v>
+        <v>0.04180332917867991</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,25 +3231,25 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002465593029455378</v>
+        <v>0.00439766900685555</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01778053084848228</v>
+        <v>-0.02164400510950222</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01462665344449953</v>
+        <v>-0.07431843443725346</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001880836763509367</v>
+        <v>0.07931548076870598</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3054775925375885</v>
+        <v>0.296562982615406</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1191082795987771</v>
+        <v>-0.1215499723112573</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05631157429709471</v>
+        <v>-0.04615068685801724</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1361613494817015</v>
+        <v>0.1926580006389432</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002294733193266919</v>
+        <v>0.003177582602861473</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04651416039464388</v>
+        <v>-0.04263038408104365</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,82 +3898,82 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1143595549848011</v>
+        <v>0.05471461186889711</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01575117735183796</v>
+        <v>-0.05482704503630392</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02237527427974123</v>
+        <v>-0.07357065881098182</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06519253337355251</v>
+        <v>-0.03147448331821597</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03098705676115913</v>
+        <v>-0.09991012211817762</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01859109739271969</v>
+        <v>-0.101501975859362</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04543501583484815</v>
+        <v>0.1221822497666515</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.02914749447021231</v>
+        <v>-0.06026335128263153</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01823960084811424</v>
+        <v>0.05123369306063968</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,25 +3982,25 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4263048451438904</v>
+        <v>0.3654634375500169</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.01190168392538317</v>
+        <v>-0.1301333533483591</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1743851813085681</v>
+        <v>-0.2056991820191984</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0180580201356551</v>
+        <v>-0.02656099983379748</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.04857090971560243</v>
+        <v>-0.01600979728977397</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0906242266745247</v>
+        <v>-0.01108802299539986</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04354354019680103</v>
+        <v>-0.01228061532869824</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.09497399068913168</v>
+        <v>0.03633665271053961</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01951117325719453</v>
+        <v>0.06776083137444615</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2253816151936224</v>
+        <v>0.2603521471197286</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.002840450104177447</v>
+        <v>-0.06351579224424758</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.00301629083487002</v>
+        <v>-0.0639484558445937</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.07325416992720549</v>
+        <v>-0.1400289331666612</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02193371116732339</v>
+        <v>0.1173358422792469</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02497859000654235</v>
+        <v>0.01627419423899944</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02413739557484641</v>
+        <v>-0.1066783576378811</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1193440142098739</v>
+        <v>0.1815827435065408</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1460855368436277</v>
+        <v>0.07251715454923678</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4144,49 +4144,49 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.05983150052954238</v>
+        <v>-0.1393693932488688</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04912537492777535</v>
+        <v>0.1282499663155051</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01998605953862091</v>
+        <v>0.02368803987247989</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.04318973332071199</v>
+        <v>-0.04677917177638483</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.007636847418410534</v>
+        <v>-0.01011070433454604</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0009421275735211564</v>
+        <v>-0.01654586286844699</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,25 +4198,25 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07059090152147374</v>
+        <v>-0.08579486975912963</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.04332018506972207</v>
+        <v>0.03890061895042522</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.01252491087629871</v>
+        <v>-0.05028948705590047</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,43 +4225,43 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04471508747890799</v>
+        <v>0.03849728205789617</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.06160340772463341</v>
+        <v>0.05027513767958633</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01418315159675655</v>
+        <v>-0.01488737880583702</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.03293130002343954</v>
+        <v>-0.09692480914731237</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07300733018646829</v>
+        <v>0.1151641828228271</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0004210113166899453</v>
+        <v>0.02252931780775963</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,31 +4270,31 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.05337754395756229</v>
+        <v>-0.08308508336476003</v>
       </c>
       <c r="EQ7" t="n">
         <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.03542810016146103</v>
+        <v>-0.08420895412283705</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.03352166635560132</v>
+        <v>0.01254461624624505</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.06690547858157071</v>
+        <v>-0.15496483531584</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03036157850960786</v>
+        <v>0.1270152445639395</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03255859580208587</v>
+        <v>0.01009310919864137</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02122799942109724</v>
+        <v>-0.06638436556937735</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.05435224605022811</v>
+        <v>0.05169288625792425</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.003926436579000847</v>
+        <v>-0.004207540589980309</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,28 +4354,28 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.006722461319961977</v>
+        <v>0.008238436596086892</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.002227462733589296</v>
+        <v>0.1412659942044857</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01448848839528436</v>
+        <v>-0.01074682566807233</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.007778256790860337</v>
+        <v>-0.1168057623419167</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.0204065869253393</v>
+        <v>0.06413901969914138</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05609020699536508</v>
+        <v>0.3750562671799201</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.006731553400387966</v>
+        <v>-0.003270938921614383</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02458099888582469</v>
+        <v>-0.1691312887647525</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01274479621649951</v>
+        <v>0.3068751233677499</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.009567471101721575</v>
+        <v>-0.07833230831337835</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004530174398476144</v>
+        <v>0.03024801259935011</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.003273098154125832</v>
+        <v>0.1320575312599535</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,52 +5048,52 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01266405712156691</v>
+        <v>-0.04342289166798524</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01808235221986935</v>
+        <v>0.04072542744265454</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0185036110552021</v>
+        <v>-0.008490837284558354</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02121369027051047</v>
+        <v>-0.2264193934406579</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.008743981067922364</v>
+        <v>0.04663252653485112</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01193527285555703</v>
+        <v>0.1194355131273919</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.003757988168317749</v>
+        <v>0.02234351964674106</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.00660101154664889</v>
+        <v>-0.07487423302540194</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,19 +5120,19 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.06479596608286443</v>
+        <v>0.5313832405649128</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.01036925531285347</v>
+        <v>-0.2555774822632096</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01404454909819755</v>
+        <v>-0.240812340153976</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,40 +5141,40 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01578535774238352</v>
+        <v>-0.006582762710391887</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.007241418936256764</v>
+        <v>-0.06702706555639101</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.004172330960384291</v>
+        <v>-0.0282481154905312</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03340112276164187</v>
+        <v>0.01523058960409389</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,13 +5183,13 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01746098336305166</v>
+        <v>0.1222367891382063</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01102426060729082</v>
+        <v>0.07856581918425666</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5198,28 +5198,28 @@
         <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02552016778466155</v>
+        <v>0.3645368836754715</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02297448037174917</v>
+        <v>-0.02121945827647664</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01895051740498904</v>
+        <v>-0.08855168641147111</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.001136988507668813</v>
+        <v>-0.1572562774490451</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.003489453634461972</v>
+        <v>0.01638082860861711</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01490556899625802</v>
+        <v>0.1075040628216449</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,52 +5252,52 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01028061799712751</v>
+        <v>-0.2019825647711698</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00569572748687843</v>
+        <v>0.2673071062270286</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03027942288783964</v>
+        <v>0.02547696053891644</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0007788391321184633</v>
+        <v>-0.1435330409726893</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.003180062225933485</v>
+        <v>0.0221765514519914</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01803994101648909</v>
+        <v>0.116886847382297</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5306,52 +5306,52 @@
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.0001501543065914756</v>
+        <v>-0.1023655803897843</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01680371776748153</v>
+        <v>-0.1016218885881402</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01347147892813701</v>
+        <v>0.1149043631848453</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.0005757055970128839</v>
+        <v>-0.1213180370440733</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0176099172881384</v>
+        <v>-0.01575012498922523</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.004516474496740992</v>
+        <v>0.02200610768545759</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02246882419558841</v>
+        <v>0.01853188698578601</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03034961973217785</v>
+        <v>-0.08594611226987579</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01490270081254944</v>
+        <v>0.05711985497502418</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0003380305499751253</v>
+        <v>-0.03360768838114778</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.004110566419791475</v>
+        <v>-0.03399808230436228</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.006637382295388534</v>
+        <v>0.03266047218606471</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.008290549833578376</v>
+        <v>-0.07487560690978716</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02479712136755212</v>
+        <v>-0.1848083094946574</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.03992440018511622</v>
+        <v>-0.1463852549081761</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.004451702128262331</v>
+        <v>-0.1689649639517236</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.004384769836463702</v>
+        <v>0.003762317363812411</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.01923683641701364</v>
+        <v>0.09502887110410443</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,34 +5471,34 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02083282581496017</v>
+        <v>-0.1326995017607324</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0310523341654663</v>
+        <v>0.131662043911962</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.005430095008258794</v>
+        <v>0.09121824673850962</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.005566260741981514</v>
+        <v>0.01434288178752227</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
@@ -5507,25 +5507,25 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.007680765987871807</v>
+        <v>-0.0437588674644841</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03130618010069067</v>
+        <v>-0.08554235885197096</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.01263648518408482</v>
+        <v>-0.07236079045810337</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.006786083501373907</v>
+        <v>0.03272138234842568</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.383560706142668</v>
+        <v>0.4195398635701382</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09779076190886185</v>
+        <v>-0.1940622196115255</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1062480879181889</v>
+        <v>-0.1029567643891346</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,25 +5575,25 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2025081759917834</v>
+        <v>0.3071124412401102</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02344589105414722</v>
+        <v>-0.06887104834230036</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.09216220952725029</v>
+        <v>-0.1211770201854508</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5605,28 +5605,28 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1005875586742831</v>
+        <v>0.09402770621750255</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.003118447783553456</v>
+        <v>-0.06202443986806605</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01680217638999137</v>
+        <v>-0.09544363655562305</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,43 +5635,43 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.08088540882238177</v>
+        <v>-0.05152267965002895</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.03509322919636021</v>
+        <v>-0.06738113774570222</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02734683607182281</v>
+        <v>-0.1206220523410288</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04950817015017756</v>
+        <v>0.1611959952068814</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03048233692859553</v>
+        <v>-0.0710915833076248</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.04663482393539276</v>
+        <v>0.047253251417878</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.411187046977498</v>
+        <v>0.4408124831387149</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.02477209548057862</v>
+        <v>-0.2000349557317669</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1038119313543385</v>
+        <v>-0.2949626250443685</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03242873186316206</v>
+        <v>-0.06289233951270734</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.02430949363568836</v>
+        <v>0.0007823661887627477</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1301334062255229</v>
+        <v>-0.02659712596666776</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05337060940467452</v>
+        <v>0.007292685061807401</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.093033764246901</v>
+        <v>0.0574991120027159</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.04711800143635538</v>
+        <v>0.05993738608609366</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,25 +5770,25 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2162459638265495</v>
+        <v>0.3465828070610165</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.01159496044515772</v>
+        <v>-0.1818349849681313</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.007687215732191862</v>
+        <v>-0.1145382901186857</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,46 +5797,46 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08634950662384012</v>
+        <v>-0.1537838081142594</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01632862301165547</v>
+        <v>0.1600865257655324</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004734716443514178</v>
+        <v>0.02461548787045875</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02071077846781871</v>
+        <v>-0.09799267904348433</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07598249753069096</v>
+        <v>0.2086454432381451</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1295632325905316</v>
+        <v>0.1137422027845533</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,55 +5845,55 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.07007101572090073</v>
+        <v>-0.1509927691800886</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0443412138974941</v>
+        <v>0.1811062859363632</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.007757530229774965</v>
+        <v>0.03777184550538275</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06349524954362808</v>
+        <v>-0.15595849567354</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.05466580901164889</v>
+        <v>0.0986425227679007</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.0114048404187319</v>
+        <v>-0.0635801906971797</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,22 +5905,22 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.04451831962517847</v>
+        <v>-0.09630824152106132</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05078749537672097</v>
+        <v>0.06324089517421669</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01403833343550674</v>
+        <v>-0.03230940821330522</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
@@ -5932,25 +5932,25 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04348691911394763</v>
+        <v>0.0353897130571518</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.01530190722358319</v>
+        <v>0.05684030484815548</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.0103601159932597</v>
+        <v>-0.01700925619826033</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,16 +5959,16 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.0487483369736842</v>
+        <v>-0.09534572803638158</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0693458095145932</v>
+        <v>0.1566389427016347</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03615777715312883</v>
+        <v>0.011966953256963</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,22 +5986,22 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.06925133461797001</v>
+        <v>-0.1151186296574244</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.06869424207499901</v>
+        <v>-0.1392833366113297</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02575295877904916</v>
+        <v>0.02501044786895775</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6013,43 +6013,43 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.08087613418741739</v>
+        <v>-0.1704104966387833</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03563388092658488</v>
+        <v>0.1757773614756193</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01809162947725996</v>
+        <v>0.02165344206930616</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.006142198269857908</v>
+        <v>-0.06446780534880235</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.04810495210678239</v>
+        <v>0.06194370740031976</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.005162947826171308</v>
+        <v>-0.007755045455501001</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6061,28 +6061,28 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01634764149349967</v>
+        <v>0.005152877472894031</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01258973972723725</v>
+        <v>0.1724920715826537</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.05020980878519361</v>
+        <v>-0.01428877887000896</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.006822307585686176</v>
+        <v>-0.1225623561123131</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.01629035226653801</v>
+        <v>0.101103009858832</v>
       </c>
       <c r="GC10" t="n">
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2394487363606619</v>
+        <v>0.1206764815640634</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02427804863629346</v>
+        <v>-0.02860861777684065</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04359335730758559</v>
+        <v>-0.04225200062637598</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1034008113000108</v>
+        <v>0.1001613247406415</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0006774987288295303</v>
+        <v>0.0009694847920433173</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03972869078679241</v>
+        <v>-0.04505405681142892</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04393748709792517</v>
+        <v>0.03253832810161995</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01640213388346165</v>
+        <v>-0.004147660315334472</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03716836833935172</v>
+        <v>-0.000782064382986249</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6767,49 +6767,49 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04599187026902475</v>
+        <v>-0.01600451088628789</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.002716775718179981</v>
+        <v>-0.06168811628440592</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0002398457050541557</v>
+        <v>-0.06975835429413629</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.01259249517925863</v>
+        <v>0.03888896664390135</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0122606295407652</v>
+        <v>-0.004079564933826339</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03007417396625421</v>
+        <v>0.03559693158013447</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,43 +6827,43 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2583109022257615</v>
+        <v>0.1467133328589827</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02945276465172876</v>
+        <v>-0.003009489259080723</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.05691293211287889</v>
+        <v>-0.07970718188416878</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03839292617255124</v>
+        <v>-0.03395186884942825</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.04339649981475312</v>
+        <v>-0.01204978664451375</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.04499530337304288</v>
+        <v>-0.01084477062248228</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1004711363150834</v>
+        <v>0.02926596689426552</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01623420546759293</v>
+        <v>0.0190778431458467</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.08360294370760073</v>
+        <v>0.0575836629074668</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,76 +6908,76 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1294351986594725</v>
+        <v>0.1217878921106221</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02493859674584921</v>
+        <v>-0.02843390008215388</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01959054750795558</v>
+        <v>-0.01133678258394781</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04390271302808058</v>
+        <v>-0.03959753011800671</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.004568875289444049</v>
+        <v>0.03264368154918242</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.002185501883351689</v>
+        <v>0.02131039816874607</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05535779582160233</v>
+        <v>-0.05258094879349149</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03408725523941308</v>
+        <v>0.03954177994406802</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.05830329543965621</v>
+        <v>0.02364954762002863</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.02933316682763779</v>
+        <v>-0.03707096709232405</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.006065549474258491</v>
+        <v>0.03635710819791239</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0005974196383930968</v>
+        <v>0.024743058594294</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,28 +7007,28 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.009635321334690297</v>
+        <v>-0.0004045054062917774</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04835572460228627</v>
+        <v>0.005413272162594625</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.003595618631672881</v>
+        <v>-0.005688323297106493</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7037,52 +7037,52 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05993834142139291</v>
+        <v>-0.03770232568288034</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.003492957242538688</v>
+        <v>-0.02312770660132538</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01084971455307731</v>
+        <v>-0.01658888926781023</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.0008174821677939163</v>
+        <v>0.04033484732243021</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.005017558660942205</v>
+        <v>0.01801750038048693</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02086382434898494</v>
+        <v>-0.0511552323765094</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02640660857914575</v>
+        <v>0.007755508918083749</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.001485459922486264</v>
+        <v>0.02627105077865468</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.04091658762316984</v>
+        <v>0.04247813364493757</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,19 +7124,19 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02163756080775064</v>
+        <v>-0.0311006193897826</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.00790756612278333</v>
+        <v>0.04084231380048546</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01302015397924713</v>
+        <v>-0.002133504944359946</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
@@ -7145,22 +7145,22 @@
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02803482642704527</v>
+        <v>-0.044654930088004</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-8.387832234335623e-05</v>
+        <v>0.04390008220941095</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01089699979392158</v>
+        <v>0.01297859257491428</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,25 +7169,25 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01552284155236092</v>
+        <v>-0.001535403351288472</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.007694894124199496</v>
+        <v>-0.00881347780686827</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.02058781069191494</v>
+        <v>-0.01768174785429841</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,25 +7196,25 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03303085630673852</v>
+        <v>0.01558456381399267</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.01421006535539592</v>
+        <v>0.04071387596447618</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01029489752183533</v>
+        <v>-0.04826952701019072</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,28 +7232,28 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.00752952422976018</v>
+        <v>-0.0177648938582192</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.01603825399834916</v>
+        <v>-0.001187953705099389</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,25 +7261,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1605399256007014</v>
+        <v>0.2367774300642678</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006401278091458649</v>
+        <v>-0.04746822210608318</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1129777584862777</v>
+        <v>-0.0961580751763431</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.09602521437486368</v>
+        <v>0.3452997436143233</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.002746214388817704</v>
+        <v>-0.1044154532583031</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.067602311936051</v>
+        <v>-0.05937445131261171</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.005347641587257957</v>
+        <v>0.06078284628117832</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01368941298279054</v>
+        <v>-0.04840040023758362</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.005106667552825693</v>
+        <v>-0.007668873730310912</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02250904304675931</v>
+        <v>-0.009081594753707654</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01664153072447774</v>
+        <v>-0.1859088046264153</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.008213214468757512</v>
+        <v>-0.02677404686713838</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,67 +7363,67 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.002050994031299848</v>
+        <v>0.04864424344955022</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01367686387297896</v>
+        <v>0.02224161261405015</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.0248580347802393</v>
+        <v>-0.02897647641596475</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1157661655634606</v>
+        <v>0.3629268199661179</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.002728993117001525</v>
+        <v>-0.1507476684279172</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.05934038852766791</v>
+        <v>-0.07816405026804917</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.05420781188733458</v>
+        <v>-0.04860938847807834</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.02108050105511207</v>
+        <v>-0.07097538804738386</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04388466506577345</v>
+        <v>-0.04591068396272943</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05513454981070844</v>
+        <v>0.09457091600208316</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03051795212441109</v>
+        <v>0.08455870873626582</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008257578638864657</v>
+        <v>-0.007213757186170615</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05345725399923137</v>
+        <v>0.2705238613169614</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.008060293865336032</v>
+        <v>-0.04288529026698193</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.01318256896963498</v>
+        <v>-0.04359329473733133</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,19 +7504,19 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.03028753042299625</v>
+        <v>-0.09418651591673065</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.004167219635404441</v>
+        <v>0.03644213072430003</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02568495419221335</v>
+        <v>0.06069839007633387</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,40 +7525,40 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.01930011614524742</v>
+        <v>-0.2365219736119024</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02440770132553023</v>
+        <v>0.1328763443227184</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01751607024815625</v>
+        <v>0.08871386174143883</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.01892324184590689</v>
+        <v>-0.08379711354978936</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,40 +7567,40 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005227843423275001</v>
+        <v>0.01798252292989297</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02457096592502378</v>
+        <v>0.05444788851634189</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.008400741825403733</v>
+        <v>0.01276836127741069</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001042181085931774</v>
+        <v>-0.03427767069027318</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.003658381387433603</v>
+        <v>0.01051699775620684</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>-0</v>
@@ -7612,115 +7612,115 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02374218466696766</v>
+        <v>-0.1210386045744082</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01377858760746663</v>
+        <v>0.06055911153727561</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.006340237613521035</v>
+        <v>-0.05309947601491272</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.000863008966240615</v>
+        <v>0.034589556269018</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01235999970556514</v>
+        <v>-0.0005239927827108273</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.005672017873137616</v>
+        <v>-0.1112997690316853</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0150112823882872</v>
+        <v>0.03581612618678985</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.005783313345189981</v>
+        <v>-0.02127373957072976</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01645489694749085</v>
+        <v>0.03997518202394117</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01700221674095626</v>
+        <v>-0.009374356729360078</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.003395472398401443</v>
+        <v>-0.04342790045132911</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03652472835416433</v>
+        <v>0.05813060642777287</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.02172432569562973</v>
+        <v>-0.101233987538667</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001725122734990073</v>
+        <v>0.01231355381630642</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02803664918674889</v>
+        <v>0.05148313086699342</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
@@ -7747,46 +7747,46 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.0004097374204507665</v>
+        <v>-0.08518414438449852</v>
       </c>
       <c r="FI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01932107035061913</v>
+        <v>0.0438219644314771</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01439179446763309</v>
+        <v>0.04016262576363552</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.00998018619863642</v>
+        <v>0.01465655550005593</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.01821284096184311</v>
+        <v>-0.0818689929547147</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001032873764034734</v>
+        <v>0.003254232288996772</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,13 +7795,13 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02131610154347048</v>
+        <v>0.00421036133868862</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01593156154605987</v>
+        <v>-0.018186794627104</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7827,28 +7827,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3340438755300984</v>
+        <v>0.2044259832215142</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09416441235929329</v>
+        <v>-0.1499949195892503</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08111904231008162</v>
+        <v>0.1484738356381059</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7860,22 +7860,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2439510602214868</v>
+        <v>0.1816371309260741</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09781014033832346</v>
+        <v>-0.1526096011519296</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1240392483071559</v>
+        <v>0.09082758766406233</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -7887,19 +7887,19 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09713897809282546</v>
+        <v>0.04132341135331856</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.03022541789480143</v>
+        <v>-0.04202783274744683</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03176677749928347</v>
+        <v>-0.02119248831408843</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
@@ -7911,16 +7911,16 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.06360513665548304</v>
+        <v>0.04793906252760022</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.04558846543739795</v>
+        <v>0.09431720592918656</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03628686871525748</v>
+        <v>0.0404507435358564</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -7929,7 +7929,7 @@
         <v>-0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -7941,49 +7941,49 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.01393048296128684</v>
+        <v>0.04898644454024619</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.03360813812514041</v>
+        <v>-0.03189092672781117</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.0666349040389084</v>
+        <v>0.007675756884389018</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1655788476775633</v>
+        <v>0.204548887728163</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.01560045412525943</v>
+        <v>-0.2180521754076369</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1642227990489524</v>
+        <v>0.01398593650154294</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,16 +7992,16 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.08415802079344267</v>
+        <v>-0.01027431528423423</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.02065491138110848</v>
+        <v>0.1268658770791365</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.08397722680833761</v>
+        <v>0.06754526825679824</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8016,49 +8016,49 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.03824546883659527</v>
+        <v>-0.07292660958878534</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05864867197975188</v>
+        <v>-0.1033937367677041</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1319784780534426</v>
+        <v>-0.1619231782428798</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.06562010493383454</v>
+        <v>0.115252496275339</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.02637017692956205</v>
+        <v>-0.1267793006879149</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09752204316394178</v>
+        <v>-0.01882849556294201</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8067,28 +8067,28 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>-0</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0.07244843748921474</v>
+        <v>-0.084090576429613</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02329392070746626</v>
+        <v>0.06870667129741444</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.004758822241223395</v>
+        <v>-0.03574906861520454</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,55 +8097,55 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01749784617661943</v>
+        <v>-0.007424025835794197</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.01983367966106321</v>
+        <v>0.1555903900229161</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.124424635823879</v>
+        <v>0.009055860972084426</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0.0556852036998321</v>
+        <v>-0.06065283368969369</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02373085443441363</v>
+        <v>0.06975408393842528</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.02886582948563264</v>
+        <v>-0.05333585445230395</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,16 +8154,16 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.03595593492190684</v>
+        <v>-0.01377954231434291</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.03963889953411061</v>
+        <v>0.02614027214942493</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.002940690298625722</v>
+        <v>-0.02090644240544691</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8175,22 +8175,22 @@
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
         <v>-0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0.003922390200513025</v>
+        <v>-0.01951380227929182</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.02451794197222971</v>
+        <v>0.06329141705962626</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1321886685058069</v>
+        <v>-0.07282662289153478</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,16 +8208,16 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.06371467190210452</v>
+        <v>0.02678921764638336</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.003426352596941492</v>
+        <v>0.04613240012478258</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.06852304782435122</v>
+        <v>0.09522376747518538</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8232,46 +8232,46 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0.1119081560373049</v>
+        <v>-0.04468971498383655</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.04692045356474604</v>
+        <v>0.05095673586784902</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0602954127677601</v>
+        <v>0.0216778793735885</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0.007098793659395275</v>
+        <v>-0.0531158761711108</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02726167522552808</v>
+        <v>0.07199894251963973</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02401818202475038</v>
+        <v>0.0150964887773984</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8280,103 +8280,103 @@
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0.06942897416451115</v>
+        <v>-0.06762701162714008</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.03771866476456184</v>
+        <v>0.1014196266391742</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.02821617680824693</v>
+        <v>-0.04026009452565392</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0.00704193741859249</v>
+        <v>-0.01823134940945335</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.008856894008899628</v>
+        <v>0.07190572377164137</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.07422186497351735</v>
+        <v>0.002997041511051565</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0.006097050541471913</v>
+        <v>0.0007384754090509363</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.006314526016534962</v>
+        <v>-0.006289059486497676</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.07116569187210106</v>
+        <v>0.1726796836335774</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.04932868410382176</v>
+        <v>-0.03030387590176661</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.04668623404967054</v>
+        <v>0.1389079032088039</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8399,19 +8399,19 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1826481596684845</v>
+        <v>0.4060691068627891</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08032578134935006</v>
+        <v>-0.02354618662433754</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06736872531833712</v>
+        <v>-0.2341676763374637</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8426,61 +8426,61 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1116275671928374</v>
+        <v>0.488532653872989</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04754352768779612</v>
+        <v>-0.1397170476705887</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.03457818057300548</v>
+        <v>-0.126548728405686</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01933184771205974</v>
+        <v>0.06108434186059048</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03079747761225275</v>
+        <v>-0.07547235993875218</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02889448121022397</v>
+        <v>0.008349281638255813</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03720111347725556</v>
+        <v>0.01338584297490699</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -8489,40 +8489,40 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02555565233532337</v>
+        <v>-0.1956713072279525</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.002689175338362269</v>
+        <v>-0.04696680353165718</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02947520652860531</v>
+        <v>0.08243517316374542</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01886626861178974</v>
+        <v>-0.0321531167467636</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.02868882975935926</v>
+        <v>-0.06345699158775629</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,91 +8531,91 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1196566491650138</v>
+        <v>0.4558884813734828</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.06333870851599262</v>
+        <v>-0.1949748227808658</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.0525529343728259</v>
+        <v>-0.1633479582898902</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.04133276380410803</v>
+        <v>0.03135632995225288</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.03363049694627965</v>
+        <v>-0.06742540389005079</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.007320072729079695</v>
+        <v>-0.07415358889139563</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05425161671165871</v>
+        <v>0.07056729676785159</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.03093411696230106</v>
+        <v>0.09434114484018057</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.02106941754549382</v>
+        <v>0.05568389754945543</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.07167540801944061</v>
+        <v>0.2707416768468819</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,16 +8624,16 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.03638090549367472</v>
+        <v>-0.07281801844231212</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.008993454881275377</v>
+        <v>-0.09117609864296113</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,7 +8642,7 @@
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02989385899019151</v>
+        <v>-0.1059165190650464</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
@@ -8651,10 +8651,10 @@
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01021494927292516</v>
+        <v>0.03608075716246708</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01933616188219326</v>
+        <v>0.08598920051560828</v>
       </c>
       <c r="CJ15" t="n">
         <v>-0</v>
@@ -8663,25 +8663,25 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.0002021315170799533</v>
+        <v>-0.2230589846646842</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.006881199366425569</v>
+        <v>0.17531060417505</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.02803817581634797</v>
+        <v>0.06222993581575119</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,25 +8690,25 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.02229336698430819</v>
+        <v>-0.1045691078984927</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.006184657115176152</v>
+        <v>0.006140800636230638</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0279594134279581</v>
+        <v>0.09383377204242571</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.01210890107323239</v>
+        <v>-0.02429771070690281</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0104433278268914</v>
+        <v>-0.02079127372754791</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.003805924586018734</v>
+        <v>0.02348599961958348</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02789640592226996</v>
+        <v>-0.09137101487089133</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,16 +8759,16 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02880624034901601</v>
+        <v>0.01826019203318983</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0261480629616661</v>
+        <v>0.09625465888438195</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,22 +8777,22 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.006299221443539146</v>
+        <v>0.03258435639705391</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.02702179783471992</v>
+        <v>-0.05956151214387194</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.01077363923906738</v>
+        <v>0.05856144337586889</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
         <v>0</v>
@@ -8801,64 +8801,64 @@
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0161834078165294</v>
+        <v>-0.03075575835699146</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0190889435468605</v>
+        <v>-0.0529689646509407</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.008616091625739248</v>
+        <v>0.05707129980580207</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-3.32959205691918e-05</v>
+        <v>-0.03404645699181105</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.01568123658661064</v>
+        <v>-0.05331391749991487</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.0291336858628004</v>
+        <v>-0.08293603910332432</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01813252205631794</v>
+        <v>-0.1167571723845735</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
@@ -8867,13 +8867,13 @@
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.003363616887637702</v>
+        <v>0.008073237323698803</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.02792489609943506</v>
+        <v>0.07920740385161186</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.02403887670226089</v>
+        <v>-0.08074588559766334</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,25 +8894,25 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04098436695841654</v>
+        <v>0.05080159321179373</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01539176755738058</v>
+        <v>-0.01473747998767071</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.001885433809501707</v>
+        <v>-0.02429197959876679</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,43 +8921,43 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.001371597360001756</v>
+        <v>0.001270735534074168</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01834722825024067</v>
+        <v>-0.01930960078890075</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.02459857039447088</v>
+        <v>-0.03987122832901713</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.02231485745684398</v>
+        <v>0.02479059824193582</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>0</v>
